--- a/stories/arbres/ATOM-SEC.RUE.002-08.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Coralie va à la boulangerie. Elle marche avec papa. Papa est l'adulte. Ils arrivent au bord. Coralie donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant. Papa dit : on attend le feu vert. Coralie sent la main de papa. Elle regarde papa. Le feu est vert. Papa dit : feu vert. On avance avec l'adulte. Coralie tient la main. Ils marchent ensemble. Le pain sent le chaud. Coralie dit : merci papa.</t>
+          <t>Coralie va à la boulangerie. Elle marche avec papa. Papa est l'adulte. Ils arrivent au bord. Coralie donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant. On attend le feu vert. Coralie sent la main de papa. Elle regarde papa. Le feu est vert. Feu vert. On avance avec l'adulte. Coralie tient la main. Ils marchent ensemble. Le pain sent le chaud. Merci papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Coralie va à la boulangerie. Elle marche avec papa. Papa est l'adulte. Ils arrivent au bord. Coralie donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant.
+papa|On attend le feu vert.
+narrateur|Coralie sent la main de papa. Elle regarde papa. Le feu est vert.
+papa|Feu vert. On avance avec l'adulte.
+narrateur|Coralie tient la main. Ils marchent ensemble. Le pain sent le chaud.
+enfant-f|Merci papa.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Coralie est avec papa. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1672,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Coralie a donné la main. Elle a attendu le feu vert. Papa, l'adulte, était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1843,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Coralie serre la main de papa. Ils tiennent le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2010,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2050,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.002-08.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 enfant-f|Merci papa.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1508,7 @@
           <t>narrateur|Coralie est avec papa. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1677,6 +1684,7 @@
           <t>narrateur|Coralie a donné la main. Elle a attendu le feu vert. Papa, l'adulte, était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1848,6 +1856,7 @@
           <t>narrateur|Coralie serre la main de papa. Ils tiennent le pain.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2015,6 +2024,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2033,7 +2043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2057,6 +2067,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2258,6 +2282,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.002-08.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Coralie attend le feu vert</t>
+          <t>Le drap de la ruelle</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorino veut le pain chaud au bout de la ruelle. Un drap claque. Au bord, il attend le feu vert, la main dans la main. Puis le pain tiède.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Coralie va à la boulangerie. Elle marche avec papa. Papa est l'adulte. Ils arrivent au bord. Coralie donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant. On attend le feu vert. Coralie sent la main de papa. Elle regarde papa. Le feu est vert. Feu vert. On avance avec l'adulte. Coralie tient la main. Ils marchent ensemble. Le pain sent le chaud. Merci papa.</t>
+          <t>Un drap blanc claque au-dessus de la ruelle. Le savon des draps sent encore le soleil. Une pince de bois pend trop bas. La pierre de la ruelle est chaude. Un géranium rouge dépasse d'une fenêtre. Ça sent le pain, tout au bout. Victorino vit ici, avec papa. Papa, le drap danse ! Oui. Il sèche au vent. Tu as vu la pince ? Elle brille. En ce moment, Victorino tend la main. La main de papa est chaude. Ils marchent sur le trottoir. Le drap claque encore une fois. Une goutte tombe sur le nez. Oh, c'est froid ! Le drap est encore mouillé. Je veux le pain chaud ! Bientôt. On reste sur le trottoir. Le beurre sent plus fort. Un chat miaule derrière un drap. Le chat ! On le verra après. Le bord du trottoir arrive. Une petite lumière rouge attend. On s'arrête. On attend le feu vert. Tu donnes la main ? Victorino serre la main. Ses pieds restent sur le trottoir. J'attends. Bravo. Le drap claque comme une voile. La pince tape contre le mur. Elle fait tic ! Oui. On attend encore ? Oui, papa. La lumière reste rouge un peu. Victorino sent le four tout près. Tu tiens bien ma main ? Oui. Puis la lumière devient verte. Feu vert. On avance avec papa. Ils avancent ensemble, tout doux. Victorino garde la main. Le pain est tout près maintenant. Ça sent trop bon ! Merci d'avoir attendu. Le drap blanc tremble encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Coralie va à la boulangerie. Elle marche avec papa. Papa est l'adulte. Ils arrivent au bord. Coralie donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant. Papa dit : on attend le &lt;emphasis level="moderate"&gt;feu&lt;/emphasis&gt; vert. Coralie sent la main de papa. Elle regarde papa. Le feu est vert. Papa dit : feu vert. On avance avec l'adulte. Coralie tient la main. Ils marchent ensemble. Le pain sent le chaud. Coralie dit : merci papa.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un drap blanc claque au-dessus de la ruelle. Le savon des draps sent encore le soleil. Une pince de bois pend trop bas. La pierre de la ruelle est chaude. Un géranium rouge dépasse d'une fenêtre. Ça sent le pain, tout au bout. Victorino vit ici, avec papa. Papa, le drap danse ! Oui. Il sèche au vent. Tu as vu la pince ? Elle brille. En ce moment, Victorino tend la main. La main de papa est chaude. Ils marchent sur le trottoir. Le drap claque encore une fois. Une goutte tombe sur le nez. Oh, c'est froid ! Le drap est encore mouillé. Je veux le pain chaud ! Bientôt. On reste sur le trottoir. Le beurre sent plus fort. Un chat miaule derrière un drap. Le chat ! On le verra après. Le bord du trottoir arrive. Une petite lumière rouge attend. On s'arrête. On attend le feu vert. Tu donnes la main ? Victorino serre la main. Ses pieds restent sur le trottoir. J'attends. Bravo. Le drap claque comme une voile. La pince tape contre le mur. Elle fait tic ! Oui. On attend encore ? Oui, papa. La lumière reste rouge un peu. Victorino sent le four tout près. Tu tiens bien ma main ? Oui. Puis la lumière devient verte. Feu vert. On avance avec papa. Ils avancent ensemble, tout doux. Victorino garde la main. Le pain est tout près maintenant. Ça sent trop bon ! Merci d'avoir attendu. Le drap blanc tremble encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,67 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Coralie va à la boulangerie. Elle marche avec papa. Papa est l'adulte. Ils arrivent au bord. Coralie donne la main. La main est dans la main. Les pieds restent sur le trottoir. Ils restent sur le trottoir en attendant.
+          <t>narrateur|Un drap blanc claque au-dessus de la ruelle.
+narrateur|Le savon des draps sent encore le soleil.
+narrateur|Une pince de bois pend trop bas.
+narrateur|La pierre de la ruelle est chaude.
+narrateur|Un géranium rouge dépasse d'une fenêtre.
+narrateur|Ça sent le pain, tout au bout.
+narrateur|Victorino vit ici, avec papa.
+enfant-m|Papa, le drap danse !
+papa|Oui.
+papa|Il sèche au vent.
+papa|Tu as vu la pince ?
+enfant-m|Elle brille.
+narrateur|En ce moment, Victorino tend la main.
+narrateur|La main de papa est chaude.
+narrateur|Ils marchent sur le trottoir.
+narrateur|Le drap claque encore une fois.
+narrateur|Une goutte tombe sur le nez.
+enfant-m|Oh, c'est froid !
+papa|Le drap est encore mouillé.
+enfant-m|Je veux le pain chaud !
+papa|Bientôt.
+papa|On reste sur le trottoir.
+narrateur|Le beurre sent plus fort.
+narrateur|Un chat miaule derrière un drap.
+enfant-m|Le chat !
+papa|On le verra après.
+narrateur|Le bord du trottoir arrive.
+narrateur|Une petite lumière rouge attend.
+papa|On s'arrête.
 papa|On attend le feu vert.
-narrateur|Coralie sent la main de papa. Elle regarde papa. Le feu est vert.
-papa|Feu vert. On avance avec l'adulte.
-narrateur|Coralie tient la main. Ils marchent ensemble. Le pain sent le chaud.
-enfant-f|Merci papa.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Tu donnes la main ?
+narrateur|Victorino serre la main.
+narrateur|Ses pieds restent sur le trottoir.
+enfant-m|J'attends.
+papa|Bravo.
+narrateur|Le drap claque comme une voile.
+narrateur|La pince tape contre le mur.
+enfant-m|Elle fait tic !
+papa|Oui.
+papa|On attend encore ?
+enfant-m|Oui, papa.
+narrateur|La lumière reste rouge un peu.
+narrateur|Victorino sent le four tout près.
+papa|Tu tiens bien ma main ?
+enfant-m|Oui.
+narrateur|Puis la lumière devient verte.
+papa|Feu vert.
+papa|On avance avec papa.
+narrateur|Ils avancent ensemble, tout doux.
+narrateur|Victorino garde la main.
+narrateur|Le pain est tout près maintenant.
+enfant-m|Ça sent trop bon !
+papa|Merci d'avoir attendu.
+narrateur|Le drap blanc tremble encore.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,12 +1409,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Coralie est avec papa. Que fait-elle ?</t>
+          <t>Victorino est avec papa. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Coralie est avec papa. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino est avec papa. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1360,12 +1424,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>feu vert</t>
+          <t>attendre le feu vert</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>feu vert | la main | avec papa | avec l'adulte | attendre</t>
+          <t>attendre | feu vert | la main | avec papa | il attend | donner la main</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1380,7 +1444,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle donne la main. Elle attend le feu vert. Que fait Coralie ?</t>
+          <t>Il attend le feu vert. Que fait Victorino ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1429,7 +1493,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1505,10 +1569,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Coralie est avec papa. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Victorino est avec papa.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,12 +1597,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Coralie a donné la main. Elle a attendu le feu vert. Papa, l'adulte, était là.</t>
+          <t>Victorino a donné la main. Il a attendu le feu vert. Ses pieds sont restés au bord. Tu as attendu le feu vert ? Oui. J'ai donné la main. Bravo, Victorino. On avance avec papa. La main de papa reste chaude. Le drap claque loin derrière. Le pain sent encore plus fort.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Coralie a donné la main. Elle a attendu le &lt;emphasis level="moderate"&gt;feu&lt;/emphasis&gt; vert. Papa, l'adulte, était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a donné la main. Il a attendu le feu vert. Ses pieds sont restés au bord. Tu as attendu le feu vert ? Oui. J'ai donné la main. Bravo, Victorino. On avance avec papa. La main de papa reste chaude. Le drap claque loin derrière. Le pain sent encore plus fort.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1594,14 +1658,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1681,10 +1745,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Coralie a donné la main. Elle a attendu le feu vert. Papa, l'adulte, était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorino a donné la main.
+narrateur|Il a attendu le feu vert.
+narrateur|Ses pieds sont restés au bord.
+papa|Tu as attendu le feu vert ?
+enfant-m|Oui.
+enfant-m|J'ai donné la main.
+papa|Bravo, Victorino.
+papa|On avance avec papa.
+narrateur|La main de papa reste chaude.
+narrateur|Le drap claque loin derrière.
+narrateur|Le pain sent encore plus fort.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1709,12 +1782,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Coralie serre la main de papa. Ils tiennent le pain.</t>
+          <t>La clochette de la boulangerie fait ding. Tu prends le pain ? Victorino tient le pain tiède. Il est chaud ! Oui. Tu as bien attendu. Le papier du pain est un peu rêche. Ça sent le beurre et la farine. On revoit le chat ? On rentre par la ruelle. Ils tiennent encore la main. Le drap blanc sèche au soleil. Le chat se lèche sur le rebord. Il est là ! Oui. Et toi, tu as gardé la main. Victorino serre le pain contre lui. La pierre de la ruelle est chaude.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Coralie serre la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de papa. Ils tiennent le pain.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La clochette de la boulangerie fait ding. Tu prends le pain ? Victorino tient le pain tiède. Il est chaud ! Oui. Tu as bien attendu. Le papier du pain est un peu rêche. Ça sent le beurre et la farine. On revoit le chat ? On rentre par la ruelle. Ils tiennent encore la main. Le drap blanc sèche au soleil. Le chat se lèche sur le rebord. Il est là ! Oui. Et toi, tu as gardé la main. Victorino serre le pain contre lui. La pierre de la ruelle est chaude.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1770,14 +1843,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1853,10 +1926,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Coralie serre la main de papa. Ils tiennent le pain.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|La clochette de la boulangerie fait ding.
+papa|Tu prends le pain ?
+narrateur|Victorino tient le pain tiède.
+enfant-m|Il est chaud !
+papa|Oui.
+papa|Tu as bien attendu.
+narrateur|Le papier du pain est un peu rêche.
+narrateur|Ça sent le beurre et la farine.
+enfant-m|On revoit le chat ?
+papa|On rentre par la ruelle.
+narrateur|Ils tiennent encore la main.
+narrateur|Le drap blanc sèche au soleil.
+narrateur|Le chat se lèche sur le rebord.
+enfant-m|Il est là !
+papa|Oui.
+papa|Et toi, tu as gardé la main.
+narrateur|Victorino serre le pain contre lui.
+narrateur|La pierre de la ruelle est chaude.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1881,12 +1970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le pain sent le four. Oui. Merci d'être resté près. Le chat cligne des yeux. Une pince brille encore. Le drap blanc sent encore le savon chaud.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le pain sent le four. Oui. Merci d'être resté près. Le chat cligne des yeux. Une pince brille encore. Le drap blanc sent encore le savon chaud.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1942,14 +2031,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2021,10 +2110,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|Le pain sent le four.
+papa|Oui.
+papa|Merci d'être resté près.
+narrateur|Le chat cligne des yeux.
+narrateur|Une pince brille encore.
+narrateur|Le drap blanc sent encore le savon chaud.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2043,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2081,6 +2174,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.002-08.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-08.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trajet vers la boulangerie</t>
+          <t>ruelle de village, linge aux fenêtres, après le soleil du matin</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Coralie, papa</t>
+          <t>Victorino, papa</t>
         </is>
       </c>
     </row>
